--- a/output/laminas_comunales/comunal_i_ingr_median_a_2018_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2018_maule.xlsx
@@ -699,7 +699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -708,310 +708,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>415000</v>
+          <t>Curepto</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chanco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>422426</v>
+          <t>Empedrado</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colbún</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>431250</v>
+          <t>Pencahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Constitución</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>506578.5</v>
+          <t>Linares</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Curepto</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>423438</v>
+          <t>Longaví</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curicó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>439626</v>
+          <t>Talca</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Empedrado</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>360000</v>
+          <t>Chanco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hualañé</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>411607</v>
+          <t>Pelluhue</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Licantén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>501250</v>
+          <t>Constitución</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linares</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>437500</v>
+          <t>Licantén</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Longaví</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>382473</v>
+          <t>Vichuquén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>490182.5</v>
+          <t>Cauquenes</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Molina</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>409915.5</v>
+          <t>Río Claro</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parral</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>400000</v>
+          <t>Pelarco</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pelarco</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>437500</v>
+          <t>San Javier</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>483334</v>
+          <t>Villa Alegre</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pencahue</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>444305</v>
+          <t>Yerbas Buenas</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rauco</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>360000</v>
+          <t>Maule</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Retiro</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>388482.5</v>
+          <t>San Rafael</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Río Claro</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>385000</v>
+          <t>Sagrada Familia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Romeral</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>401313.5</v>
+          <t>Retiro</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>409470</v>
+          <t>Curicó</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Clemente</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>428900</v>
+          <t>Molina</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Javier</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>423875</v>
+          <t>Colbún</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Rafael</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>452600</v>
+          <t>San Clemente</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Talca</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>519660</v>
+          <t>Hualañé</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Teno</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>392402</v>
+          <t>Rauco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>403817</v>
+          <t>Teno</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>416250</v>
+          <t>Romeral</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>386817.5</v>
+          <t>Parral</t>
+        </is>
       </c>
     </row>
   </sheetData>
